--- a/docs/data/jp/xlsx/7735.xlsx
+++ b/docs/data/jp/xlsx/7735.xlsx
@@ -16101,7 +16101,7 @@
     <row r="236">
       <c r="A236" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Net Defined Benefit Asset And Liability Ope CF</t>
+          <t>퇴직급여 관련 자산·부채 증감액</t>
         </is>
       </c>
       <c r="C236" s="20" t="n">
@@ -17387,7 +17387,7 @@
     <row r="259">
       <c r="A259" s="18" t="inlineStr">
         <is>
-          <t>Contribution In Connection With The Shift To ADefined Contribution Pension Plan Ope CF</t>
+          <t>확정기여연금 제도 전환에 따른 출연액</t>
         </is>
       </c>
       <c r="O259" s="20" t="n">
@@ -18062,7 +18062,7 @@
     <row r="271">
       <c r="A271" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Shares Of Subsidiaries Resulting In Change In Scope Of Consolidation Inv CF</t>
+          <t>연결 범위 변경을 수반하는 관계회사 주식 매각 수입</t>
         </is>
       </c>
       <c r="D271" s="20" t="n">
@@ -18595,7 +18595,7 @@
     <row r="285">
       <c r="A285" s="18" t="inlineStr">
         <is>
-          <t>Net Decrease Increase In Treasury Stock Fin CF</t>
+          <t>자기주식 순증감액(△는 증가)</t>
         </is>
       </c>
       <c r="C285" s="20" t="n">
